--- a/VNFramework/Assets/StreamingAssets/story/zh/Test3.xlsx
+++ b/VNFramework/Assets/StreamingAssets/story/zh/Test3.xlsx
@@ -107,10 +107,14 @@
     <t>choice</t>
   </si>
   <si>
-    <t>Choice 111</t>
-  </si>
-  <si>
-    <t>Choice 112</t>
+    <t>Choice 111
+Choice 112
+Choice 12</t>
+  </si>
+  <si>
+    <t>111
+112
+12</t>
   </si>
 </sst>
 </file>
@@ -724,8 +728,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1101,16 +1108,16 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1142,16 +1149,16 @@
       <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>1</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="2">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="2">
         <v>0</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1183,19 +1190,19 @@
       <c r="L3" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="2">
         <f>IF(E2&lt;&gt;"",E2,M2)</f>
         <v>1</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="2">
         <f>IF(F2&lt;&gt;"",F2,N2)</f>
         <v>1</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="2">
         <f>IF(H2&lt;&gt;"",H2,O2)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <f>IF(K2&lt;&gt;"",K2,P2)</f>
         <v>0</v>
       </c>
@@ -1231,19 +1238,19 @@
       <c r="L4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="2">
         <f>IF(E3&lt;&gt;"",E3,M3)</f>
         <v>1</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4" s="2">
         <f>IF(F3&lt;&gt;"",F3,N3)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4" s="2">
         <f>IF(H3&lt;&gt;"",H3,O3)</f>
         <v>0</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <f>IF(K3&lt;&gt;"",K3,P3)</f>
         <v>0</v>
       </c>
@@ -1270,38 +1277,32 @@
       <c r="L5" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="2">
         <f>IF(E4&lt;&gt;"",E4,M4)</f>
         <v>3</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <f>IF(F4&lt;&gt;"",F4,N4)</f>
         <v>1</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O5" s="2">
         <f>IF(H4&lt;&gt;"",H4,O4)</f>
         <v>0</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <f>IF(K4&lt;&gt;"",K4,P4)</f>
         <v>-540</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" ht="45" spans="1:3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E6">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
